--- a/docs/BOM.xlsx
+++ b/docs/BOM.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevHome\Lumos Ultra Exhaust\LumosAir\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DB738CE-8FBC-45C4-960F-7C374A4388DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49EA650-BE9C-43D9-9804-75C953D3EC65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6810" yWindow="3090" windowWidth="28800" windowHeight="15370" xr2:uid="{371F08E5-8B75-4CD8-A419-3F8DDBC3B8F1}"/>
+    <workbookView xWindow="7110" yWindow="3050" windowWidth="28800" windowHeight="15370" xr2:uid="{371F08E5-8B75-4CD8-A419-3F8DDBC3B8F1}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="108">
   <si>
     <t>Item</t>
   </si>
@@ -85,9 +98,6 @@
     <t>pitot (laser node)</t>
   </si>
   <si>
-    <t>35-50</t>
-  </si>
-  <si>
     <t>29 x 18 body; 24 tall incl. barbs; barbs 5.2 OD / 12.6 apart; 4 pins at 2.0 pitch; 2x M2.5 holes 24 apart</t>
   </si>
   <si>
@@ -335,6 +345,18 @@
   </si>
   <si>
     <t>See DESIGN.md section 4 before choosing</t>
+  </si>
+  <si>
+    <t>Sourced?</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>2.0 Inch LCD Display Module, 240x320 Full Color TFT IPS Screen</t>
+  </si>
+  <si>
+    <t>Ordered?</t>
   </si>
 </sst>
 </file>
@@ -818,9 +840,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1196,626 +1221,701 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E94848BD-8383-464A-B29A-4810314F6AF0}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="79.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="51.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="81.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="100.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="140.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="214.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.36328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="51.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="81.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="100.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="140.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="214.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1">
-        <v>46246</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" s="2">
+        <f xml:space="preserve"> 14.99/4</f>
+        <v>3.7475000000000001</v>
+      </c>
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1">
-        <v>46150</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" s="2">
+        <f xml:space="preserve"> 14.99/4</f>
+        <v>3.7475000000000001</v>
+      </c>
+      <c r="G3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2">
+        <f>17.99/2</f>
+        <v>8.9949999999999992</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F5" s="2">
+        <f>31.25/2</f>
+        <v>15.625</v>
+      </c>
+      <c r="G5" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H5" t="s">
         <v>22</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I5" t="s">
         <v>23</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J5" t="s">
         <v>24</v>
       </c>
-      <c r="H4" t="s">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" t="s">
         <v>26</v>
       </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="F6" s="2">
+        <f xml:space="preserve"> 71.9/6</f>
+        <v>11.983333333333334</v>
+      </c>
+      <c r="G6" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="1">
-        <v>46249</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="H6" t="s">
         <v>28</v>
       </c>
-      <c r="F5" t="s">
+      <c r="I6" t="s">
         <v>29</v>
       </c>
-      <c r="G5" t="s">
+      <c r="J6" t="s">
         <v>30</v>
       </c>
-      <c r="H5" t="s">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>38</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="2">
+        <f>9.99/6</f>
+        <v>1.665</v>
+      </c>
+      <c r="G7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="1">
-        <v>46157</v>
-      </c>
-      <c r="E7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
       <c r="H7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
+      <c r="C8" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
+        <v>32</v>
+      </c>
+      <c r="F8" s="2">
+        <f>18.99/3</f>
+        <v>6.3299999999999992</v>
       </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="I8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
+      <c r="C9" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
+        <v>43</v>
+      </c>
+      <c r="F9" s="2">
+        <f>7.99/50</f>
+        <v>0.1598</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+      <c r="I9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="1">
-        <v>46310</v>
-      </c>
       <c r="E10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
         <v>52</v>
       </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" t="s">
-        <v>52</v>
-      </c>
-      <c r="H10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="2">
+        <v>46310</v>
+      </c>
+      <c r="G11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D11" t="s">
+      <c r="G12" t="s">
         <v>59</v>
       </c>
-      <c r="E11" t="s">
+      <c r="H12" t="s">
         <v>60</v>
       </c>
-      <c r="F11" t="s">
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" t="s">
         <v>61</v>
       </c>
-      <c r="G11" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" t="s">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="G13" t="s">
         <v>64</v>
       </c>
-      <c r="E12" t="s">
+      <c r="H13" t="s">
         <v>65</v>
       </c>
-      <c r="F12" t="s">
+      <c r="I13" t="s">
         <v>66</v>
       </c>
-      <c r="G12" t="s">
+      <c r="J13" t="s">
         <v>67</v>
       </c>
-      <c r="H12" t="s">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E14" t="s">
         <v>69</v>
       </c>
-      <c r="B13">
+      <c r="F14" s="2">
+        <f xml:space="preserve"> 9.59/30</f>
+        <v>0.31966666666666665</v>
+      </c>
+      <c r="G14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="2">
+        <f>13.99/6</f>
+        <v>2.3316666666666666</v>
+      </c>
+      <c r="G15" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" t="s">
+        <v>51</v>
+      </c>
+      <c r="I15" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19">
         <v>4</v>
       </c>
-      <c r="C13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="E19" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="2">
         <v>46025</v>
       </c>
-      <c r="E14" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B15">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16">
-        <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17">
-        <v>3</v>
-      </c>
-      <c r="C17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18">
-        <v>4</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="G19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" t="s">
+        <v>51</v>
+      </c>
+      <c r="I19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="1">
-        <v>46025</v>
-      </c>
-      <c r="E18" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H18" t="s">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" t="s">
-        <v>52</v>
-      </c>
-      <c r="H19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>88</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" t="s">
-        <v>90</v>
-      </c>
       <c r="E20" t="s">
-        <v>52</v>
-      </c>
-      <c r="F20" t="s">
-        <v>52</v>
+        <v>85</v>
+      </c>
+      <c r="F20" s="2">
+        <v>3</v>
       </c>
       <c r="G20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H20" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="I20" t="s">
+        <v>51</v>
+      </c>
+      <c r="J20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21">
-        <v>10</v>
-      </c>
       <c r="E21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" t="s">
-        <v>52</v>
+        <v>88</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="G21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+      <c r="I21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="2">
+        <v>10</v>
+      </c>
+      <c r="G22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" t="s">
+        <v>51</v>
+      </c>
+      <c r="J22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="2">
+        <v>5</v>
+      </c>
+      <c r="G23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23" t="s">
+        <v>51</v>
+      </c>
+      <c r="I23" t="s">
+        <v>51</v>
+      </c>
+      <c r="J23" t="s">
         <v>96</v>
       </c>
-      <c r="D22">
-        <v>5</v>
-      </c>
-      <c r="E22" t="s">
-        <v>52</v>
-      </c>
-      <c r="F22" t="s">
-        <v>52</v>
-      </c>
-      <c r="G22" t="s">
-        <v>52</v>
-      </c>
-      <c r="H22" t="s">
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="E24" t="s">
         <v>98</v>
       </c>
-      <c r="B23">
-        <v>2</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" t="s">
+        <v>51</v>
+      </c>
+      <c r="I24" t="s">
+        <v>51</v>
+      </c>
+      <c r="J24" t="s">
         <v>99</v>
       </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" t="s">
-        <v>52</v>
-      </c>
-      <c r="F23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23" t="s">
-        <v>52</v>
-      </c>
-      <c r="H23" t="s">
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
         <v>101</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="F25" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D24" t="s">
+      <c r="G25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" t="s">
         <v>103</v>
-      </c>
-      <c r="E24" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24" t="s">
-        <v>52</v>
-      </c>
-      <c r="H24" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>